--- a/public/plantilla-estudiantes.xlsx
+++ b/public/plantilla-estudiantes.xlsx
@@ -397,39 +397,44 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B3"/>
-  <cols>
-    <col min="1" max="1" width="28.83203125" customWidth="1"/>
-    <col min="2" max="2" width="32.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:C3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
+        <v>RUT</v>
+      </c>
+      <c r="B1" t="str">
         <v>Nombre completo</v>
       </c>
-      <c r="B1" t="str">
+      <c r="C1" t="str">
         <v>Correo electronico</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
+        <v>12345678-9</v>
+      </c>
+      <c r="B2" t="str">
         <v>Ana Torres</v>
       </c>
-      <c r="B2" t="str">
+      <c r="C2" t="str">
         <v>ana.torres@correo.com</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
+        <v>23456789-0</v>
+      </c>
+      <c r="B3" t="str">
         <v>Luis Perez</v>
       </c>
-      <c r="B3" t="str">
+      <c r="C3" t="str">
         <v>luis.perez@correo.com</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C3"/>
   </ignoredErrors>
 </worksheet>
 </file>